--- a/docs/StructureDefinition-HAHAdmissionEncounter.xlsx
+++ b/docs/StructureDefinition-HAHAdmissionEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4118" uniqueCount="615">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T17:33:17+08:00</t>
+    <t>2026-09-29T04:34:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>表達本次在宅急症的整段照護，供每次訪視透過 partOf 參照。IMP 表示本資料集的在宅住院照護分類，不代表照護地點在醫院。</t>
+    <t>表達本次在宅急症的整段照護，供每次訪視透過 partOf 參照。IMP 表示在宅住院照護分類，location 記錄照護地點。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -791,10 +791,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>就醫的分類；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -836,9 +833,6 @@
   <si>
     <t>inpatient ｜ outpatient ｜ ambulatory ｜ emergency +.
 住院病人 ｜ 門診病人 ｜ 非臥床（可行走）病人醫療服務 ｜ 急診 +</t>
-  </si>
-  <si>
-    <t>就醫類別；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -1205,10 +1199,7 @@
     <t>表明就醫的急迫性</t>
   </si>
   <si>
-    <t>表明就醫的迫切性；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1699,10 +1690,7 @@
     <t>此次住院是否為再入院，如果知道的話，請說明原因。</t>
   </si>
   <si>
-    <t>這次住院就醫的再入院原因；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -2251,17 +2239,17 @@
   <dimension ref="A1:AN114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.83984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.52734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.47265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="27.953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="230.44140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="230.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2270,26 +2258,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="125.0625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="125.8359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="163.86328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="161.73828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5321,11 +5309,9 @@
       <c r="X27" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5361,21 +5347,21 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5401,10 +5387,10 @@
         <v>228</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5455,7 +5441,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5484,10 +5470,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5596,10 +5582,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5710,10 +5696,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5826,10 +5812,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5852,13 +5838,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5887,11 +5873,9 @@
       <c r="X32" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y32" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5909,7 +5893,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -5938,10 +5922,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5967,10 +5951,10 @@
         <v>203</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6021,7 +6005,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -6050,10 +6034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6079,13 +6063,13 @@
         <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6096,29 +6080,29 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y34" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="T34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Y34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
       </c>
@@ -6135,7 +6119,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6150,24 +6134,24 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6193,10 +6177,10 @@
         <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6223,13 +6207,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6247,7 +6231,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6262,7 +6246,7 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>157</v>
@@ -6271,15 +6255,15 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6305,10 +6289,10 @@
         <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6388,10 +6372,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6417,10 +6401,10 @@
         <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6500,10 +6484,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6529,16 +6513,16 @@
         <v>244</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6575,7 +6559,7 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
@@ -6585,7 +6569,7 @@
         <v>162</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6603,24 +6587,24 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -6645,16 +6629,16 @@
         <v>244</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6683,7 +6667,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6701,7 +6685,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6719,21 +6703,21 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6759,10 +6743,10 @@
         <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6842,10 +6826,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6871,13 +6855,13 @@
         <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6956,10 +6940,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6985,16 +6969,16 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7004,7 +6988,7 @@
         <v>20</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>20</v>
@@ -7043,7 +7027,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7061,21 +7045,21 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7101,13 +7085,13 @@
         <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7157,7 +7141,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7175,21 +7159,21 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7215,14 +7199,14 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7271,7 +7255,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7289,21 +7273,21 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7329,14 +7313,14 @@
         <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7385,7 +7369,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7403,21 +7387,21 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7440,19 +7424,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7501,7 +7485,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7519,24 +7503,24 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
@@ -7561,16 +7545,16 @@
         <v>244</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7599,7 +7583,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7617,7 +7601,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7635,21 +7619,21 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7675,10 +7659,10 @@
         <v>153</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7758,10 +7742,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7787,13 +7771,13 @@
         <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7872,10 +7856,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7901,16 +7885,16 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7920,7 +7904,7 @@
         <v>20</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>20</v>
@@ -7959,7 +7943,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7977,21 +7961,21 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8017,13 +8001,13 @@
         <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8073,7 +8057,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8091,21 +8075,21 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8131,14 +8115,14 @@
         <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8187,7 +8171,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8205,21 +8189,21 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8245,14 +8229,14 @@
         <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8301,7 +8285,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8319,21 +8303,21 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8356,19 +8340,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8417,7 +8401,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8435,24 +8419,24 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>20</v>
@@ -8477,16 +8461,16 @@
         <v>244</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8515,7 +8499,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8533,7 +8517,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8551,21 +8535,21 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8591,10 +8575,10 @@
         <v>153</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8674,10 +8658,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8703,13 +8687,13 @@
         <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8788,10 +8772,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8817,16 +8801,16 @@
         <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8836,7 +8820,7 @@
         <v>20</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>20</v>
@@ -8875,7 +8859,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8893,21 +8877,21 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8933,13 +8917,13 @@
         <v>153</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8989,7 +8973,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9007,21 +8991,21 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9047,14 +9031,14 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9103,7 +9087,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9121,21 +9105,21 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9161,14 +9145,14 @@
         <v>153</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9217,7 +9201,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9235,21 +9219,21 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9272,19 +9256,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9333,7 +9317,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9351,21 +9335,21 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9391,16 +9375,16 @@
         <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9449,7 +9433,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9467,21 +9451,21 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9507,10 +9491,10 @@
         <v>175</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9537,13 +9521,11 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9561,7 +9543,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9579,25 +9561,25 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9616,16 +9598,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9675,7 +9657,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9690,24 +9672,24 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9730,13 +9712,13 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9787,7 +9769,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9802,28 +9784,28 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9842,13 +9824,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9899,7 +9881,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9914,10 +9896,10 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9928,10 +9910,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9957,10 +9939,10 @@
         <v>228</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10011,7 +9993,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10026,24 +10008,24 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10152,10 +10134,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10266,10 +10248,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10382,10 +10364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10411,13 +10393,13 @@
         <v>175</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10446,10 +10428,10 @@
         <v>180</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10467,7 +10449,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10482,24 +10464,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10525,10 +10507,10 @@
         <v>203</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10579,7 +10561,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10597,21 +10579,21 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10634,13 +10616,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10691,7 +10673,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10706,24 +10688,24 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10746,13 +10728,13 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10803,7 +10785,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10818,24 +10800,24 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10861,13 +10843,13 @@
         <v>203</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10917,7 +10899,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10932,24 +10914,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11058,10 +11040,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11172,10 +11154,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11198,16 +11180,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11257,7 +11239,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11266,7 +11248,7 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>99</v>
@@ -11275,21 +11257,21 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11312,23 +11294,23 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>20</v>
@@ -11373,7 +11355,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11382,7 +11364,7 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
@@ -11391,21 +11373,21 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11428,16 +11410,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11487,7 +11469,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11502,28 +11484,28 @@
         <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11545,13 +11527,13 @@
         <v>175</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11580,10 +11562,10 @@
         <v>112</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11601,7 +11583,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11616,28 +11598,28 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11656,16 +11638,16 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11715,7 +11697,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11730,24 +11712,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11773,10 +11755,10 @@
         <v>228</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11827,7 +11809,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11845,7 +11827,7 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>20</v>
@@ -11856,10 +11838,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11968,10 +11950,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12082,10 +12064,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12198,14 +12180,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12224,16 +12206,16 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12283,7 +12265,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>87</v>
@@ -12298,24 +12280,24 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12341,10 +12323,10 @@
         <v>175</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12374,10 +12356,10 @@
         <v>112</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12395,7 +12377,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12424,10 +12406,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12450,13 +12432,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12507,7 +12489,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12525,7 +12507,7 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
@@ -12536,10 +12518,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12562,16 +12544,16 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12621,7 +12603,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12639,7 +12621,7 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>20</v>
@@ -12650,10 +12632,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12679,13 +12661,13 @@
         <v>228</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12735,7 +12717,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12753,7 +12735,7 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>20</v>
@@ -12764,10 +12746,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12876,10 +12858,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12990,10 +12972,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13106,10 +13088,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13135,10 +13117,10 @@
         <v>146</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13189,7 +13171,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13213,15 +13195,15 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13244,13 +13226,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13301,7 +13283,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13319,7 +13301,7 @@
         <v>20</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>20</v>
@@ -13330,10 +13312,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13359,10 +13341,10 @@
         <v>175</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13392,10 +13374,10 @@
         <v>112</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>20</v>
@@ -13413,7 +13395,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13431,21 +13413,21 @@
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13471,10 +13453,10 @@
         <v>175</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13501,13 +13483,11 @@
         <v>20</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -13525,7 +13505,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13549,15 +13529,15 @@
         <v>20</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13583,16 +13563,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -13617,13 +13597,13 @@
         <v>20</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -13641,7 +13621,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13659,21 +13639,21 @@
         <v>20</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13699,10 +13679,10 @@
         <v>175</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13732,10 +13712,10 @@
         <v>112</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -13753,7 +13733,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13771,21 +13751,21 @@
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13811,10 +13791,10 @@
         <v>175</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13844,10 +13824,10 @@
         <v>112</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -13865,7 +13845,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13883,21 +13863,21 @@
         <v>20</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13920,13 +13900,13 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13977,7 +13957,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13995,21 +13975,21 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14035,10 +14015,10 @@
         <v>175</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14065,13 +14045,13 @@
         <v>20</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
@@ -14089,7 +14069,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14107,21 +14087,21 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14147,13 +14127,13 @@
         <v>228</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14203,7 +14183,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14221,7 +14201,7 @@
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>20</v>
@@ -14232,10 +14212,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14344,10 +14324,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14458,10 +14438,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14574,10 +14554,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14600,13 +14580,13 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14657,7 +14637,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -14672,24 +14652,24 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14715,13 +14695,13 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14750,10 +14730,10 @@
         <v>169</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>20</v>
@@ -14771,7 +14751,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14789,7 +14769,7 @@
         <v>20</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>20</v>
@@ -14800,10 +14780,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14829,13 +14809,13 @@
         <v>175</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14861,13 +14841,13 @@
         <v>20</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -14885,7 +14865,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14914,10 +14894,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14943,10 +14923,10 @@
         <v>203</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14997,7 +14977,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15015,7 +14995,7 @@
         <v>20</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>20</v>
@@ -15026,10 +15006,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15052,13 +15032,13 @@
         <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15109,7 +15089,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15124,24 +15104,24 @@
         <v>99</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15164,16 +15144,16 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15223,7 +15203,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15238,10 +15218,10 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>20</v>
